--- a/VerveStacks_NOR_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_NOR_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F6A91A-5A11-4B00-B737-63CFAFE8D228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC233D4-294B-4246-823A-C65B1034D5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10257" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10265" uniqueCount="273">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -825,19 +825,22 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S02aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S04aH02,S02aH04,S02aH05,S04aH06,S01aH06,S02aH03,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S03aH02,S03aH03</t>
+    <t>S01aH03,S04aH03,S03aH03,S02aH06,S03aH05,S03aH08,S04aH07,S03aH02,S03aH04,S02aH04,S02aH05,S02aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH02,S04aH04,S04aH02,S01aH06,S02aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S02aH10,S03aH01,S03aH09,S01aH02,S02aH09,S04aH09,S01aH10,S03aH02,S03aH08,S03aH10,S01aH01,S04aH01,S01aH09,S01aH08,S02aH08,S04aH02,S02aH02,S04aH10,S04aH08</t>
+    <t>S02aH01,S02aH10,S02aH02,S04aH10,S03aH09,S04aH02,S02aH09,S04aH09,S03aH08,S03aH10,S03aH01,S01aH09,S01aH02,S01aH08,S02aH08,S01aH10,S03aH02,S04aH08,S01aH01,S04aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
   </si>
   <si>
     <t>elc_industry</t>
+  </si>
+  <si>
+    <t>het_buildings</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -1397,7 +1400,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S02aH10,S03aH01,S03aH09,S01aH02,S02aH09,S04aH09,S01aH10,S03aH02,S03aH08,S03aH10,S01aH01,S04aH01,S01aH09,S01aH08,S02aH08,S04aH02,S02aH02,S04aH10,S04aH08</v>
+        <v>S02aH01,S02aH10,S02aH02,S04aH10,S03aH09,S04aH02,S02aH09,S04aH09,S03aH08,S03aH10,S03aH01,S01aH09,S01aH02,S01aH08,S02aH08,S01aH10,S03aH02,S04aH08,S01aH01,S04aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1429,7 +1432,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S02aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S04aH02,S02aH04,S02aH05,S04aH06,S01aH06,S02aH03,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S03aH02,S03aH03</v>
+        <v>S01aH03,S04aH03,S03aH03,S02aH06,S03aH05,S03aH08,S04aH07,S03aH02,S03aH04,S02aH04,S02aH05,S02aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH02,S04aH04,S04aH02,S01aH06,S02aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1536,7 +1539,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7304DD5B-B958-4F46-85A5-A0F2A28E7268}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3697255-CF0B-4990-BBFB-9173B009AF66}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1670,7 +1673,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D52EB9-7EEC-4102-A6D8-30DB87CE0E34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D358B02-5B7F-4420-A50B-2F68AC553837}">
   <dimension ref="B9:O1450"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38692,7 +38695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D00DCE-876E-473B-ACAA-16B3EF4F69F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3FE91D8-B6E5-421F-87FE-FB5139D11627}">
   <dimension ref="B9:HS81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84926,7 +84929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126D05EC-26BB-4E04-9010-AA3FEA1E6192}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D491BA-8F8D-47D4-BAFC-E344FE3FA3A4}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84980,19 +84983,19 @@
         <v>56</v>
       </c>
       <c r="N10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q10" t="s">
         <v>56</v>
       </c>
       <c r="R10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -85036,7 +85039,7 @@
         <v>0.51333333333333331</v>
       </c>
       <c r="S11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -85077,10 +85080,10 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.48293333333333338</v>
+        <v>0.48293333333333327</v>
       </c>
       <c r="S12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -85124,7 +85127,7 @@
         <v>0.40433333333333338</v>
       </c>
       <c r="S13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -85168,7 +85171,7 @@
         <v>0.4665333333333333</v>
       </c>
       <c r="S14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -85212,7 +85215,7 @@
         <v>0.5678333333333333</v>
       </c>
       <c r="S15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -85256,7 +85259,7 @@
         <v>0.44270000000000004</v>
       </c>
       <c r="S16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -85300,7 +85303,7 @@
         <v>0.37896666666666667</v>
       </c>
       <c r="S17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -85344,7 +85347,7 @@
         <v>0.43433333333333329</v>
       </c>
       <c r="S18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -85388,7 +85391,7 @@
         <v>0.49553333333333333</v>
       </c>
       <c r="S19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -85432,7 +85435,7 @@
         <v>0.42123333333333335</v>
       </c>
       <c r="S20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -85476,7 +85479,7 @@
         <v>0.39156666666666667</v>
       </c>
       <c r="S21" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -85520,7 +85523,7 @@
         <v>0.38286666666666669</v>
       </c>
       <c r="S22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
@@ -85564,7 +85567,7 @@
         <v>0.68703333333333327</v>
       </c>
       <c r="S23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
@@ -85608,7 +85611,7 @@
         <v>0.57043333333333335</v>
       </c>
       <c r="S24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
@@ -85652,7 +85655,7 @@
         <v>0.51189999999999991</v>
       </c>
       <c r="S25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
@@ -85696,7 +85699,7 @@
         <v>0.57546666666666668</v>
       </c>
       <c r="S26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
@@ -85740,7 +85743,7 @@
         <v>0.50803333333333323</v>
       </c>
       <c r="S27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
@@ -85781,10 +85784,10 @@
         <v>42</v>
       </c>
       <c r="R28">
-        <v>0.42380000000000001</v>
+        <v>0.42379999999999995</v>
       </c>
       <c r="S28" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
@@ -85828,7 +85831,7 @@
         <v>0.39040000000000002</v>
       </c>
       <c r="S29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
@@ -85872,7 +85875,7 @@
         <v>0.41570000000000001</v>
       </c>
       <c r="S30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
@@ -85916,7 +85919,7 @@
         <v>0.67649999999999999</v>
       </c>
       <c r="S31" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
@@ -85960,7 +85963,7 @@
         <v>0.56376666666666664</v>
       </c>
       <c r="S32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.45">
@@ -86004,7 +86007,7 @@
         <v>0.46443333333333331</v>
       </c>
       <c r="S33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="3:19" x14ac:dyDescent="0.45">
@@ -86048,7 +86051,7 @@
         <v>0.54683333333333328</v>
       </c>
       <c r="S34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="3:19" x14ac:dyDescent="0.45">
@@ -86092,7 +86095,7 @@
         <v>0.64013333333333333</v>
       </c>
       <c r="S35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="3:19" x14ac:dyDescent="0.45">
@@ -86136,7 +86139,7 @@
         <v>0.52859999999999996</v>
       </c>
       <c r="S36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="3:19" x14ac:dyDescent="0.45">
@@ -86180,7 +86183,7 @@
         <v>0.4830666666666667</v>
       </c>
       <c r="S37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="3:19" x14ac:dyDescent="0.45">
@@ -86224,7 +86227,7 @@
         <v>0.58586666666666665</v>
       </c>
       <c r="S38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="3:19" x14ac:dyDescent="0.45">
@@ -86268,7 +86271,7 @@
         <v>0.63506666666666678</v>
       </c>
       <c r="S39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="3:19" x14ac:dyDescent="0.45">
@@ -86309,10 +86312,10 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.54620000000000002</v>
+        <v>0.54619999999999991</v>
       </c>
       <c r="S40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="3:19" x14ac:dyDescent="0.45">
@@ -86356,7 +86359,7 @@
         <v>0.4548666666666667</v>
       </c>
       <c r="S41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="3:19" x14ac:dyDescent="0.45">
@@ -86400,7 +86403,7 @@
         <v>0.53326666666666667</v>
       </c>
       <c r="S42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.45">
@@ -86444,7 +86447,7 @@
         <v>0.64080000000000004</v>
       </c>
       <c r="S43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="3:19" x14ac:dyDescent="0.45">
@@ -86488,7 +86491,7 @@
         <v>0.53003333333333336</v>
       </c>
       <c r="S44" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="3:19" x14ac:dyDescent="0.45">
@@ -86532,7 +86535,7 @@
         <v>0.41166666666666663</v>
       </c>
       <c r="S45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="3:19" x14ac:dyDescent="0.45">
@@ -86576,7 +86579,7 @@
         <v>0.51266666666666671</v>
       </c>
       <c r="S46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="3:19" x14ac:dyDescent="0.45">
@@ -86620,7 +86623,7 @@
         <v>0.58139999999999992</v>
       </c>
       <c r="S47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="3:19" x14ac:dyDescent="0.45">
@@ -86664,7 +86667,7 @@
         <v>0.4685333333333333</v>
       </c>
       <c r="S48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="3:19" x14ac:dyDescent="0.45">
@@ -86705,10 +86708,10 @@
         <v>44</v>
       </c>
       <c r="R49">
-        <v>0.41726666666666667</v>
+        <v>0.41726666666666662</v>
       </c>
       <c r="S49" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="3:19" x14ac:dyDescent="0.45">
@@ -86752,7 +86755,7 @@
         <v>0.44283333333333336</v>
       </c>
       <c r="S50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="3:19" x14ac:dyDescent="0.45">
@@ -86775,7 +86778,7 @@
         <v>0.64950000000000008</v>
       </c>
       <c r="S51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="3:19" x14ac:dyDescent="0.45">
@@ -86798,7 +86801,7 @@
         <v>0.52576666666666672</v>
       </c>
       <c r="S52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="3:19" x14ac:dyDescent="0.45">
@@ -86821,7 +86824,7 @@
         <v>0.38569999999999999</v>
       </c>
       <c r="S53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="3:19" x14ac:dyDescent="0.45">
@@ -86844,7 +86847,7 @@
         <v>0.48826666666666663</v>
       </c>
       <c r="S54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="3:19" x14ac:dyDescent="0.45">
@@ -86867,7 +86870,7 @@
         <v>0.59670000000000001</v>
       </c>
       <c r="S55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.45">
@@ -86890,7 +86893,7 @@
         <v>0.49499999999999994</v>
       </c>
       <c r="S56" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="3:19" x14ac:dyDescent="0.45">
@@ -86913,7 +86916,7 @@
         <v>0.40076666666666672</v>
       </c>
       <c r="S57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.45">
@@ -86933,10 +86936,10 @@
         <v>46</v>
       </c>
       <c r="R58">
-        <v>0.52036666666666664</v>
+        <v>0.52036666666666676</v>
       </c>
       <c r="S58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="3:19" x14ac:dyDescent="0.45">
@@ -86959,7 +86962,7 @@
         <v>0.65393333333333326</v>
       </c>
       <c r="S59" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="3:19" x14ac:dyDescent="0.45">
@@ -86982,7 +86985,7 @@
         <v>0.47013333333333329</v>
       </c>
       <c r="S60" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="3:19" x14ac:dyDescent="0.45">
@@ -87005,7 +87008,7 @@
         <v>0.45906666666666668</v>
       </c>
       <c r="S61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="3:19" x14ac:dyDescent="0.45">
@@ -87028,7 +87031,7 @@
         <v>0.46543333333333337</v>
       </c>
       <c r="S62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="3:19" x14ac:dyDescent="0.45">
@@ -87051,7 +87054,7 @@
         <v>0.57210000000000005</v>
       </c>
       <c r="S63" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="3:19" x14ac:dyDescent="0.45">
@@ -87074,7 +87077,7 @@
         <v>0.47480000000000006</v>
       </c>
       <c r="S64" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="8:19" x14ac:dyDescent="0.45">
@@ -87097,7 +87100,7 @@
         <v>0.40796666666666664</v>
       </c>
       <c r="S65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="8:19" x14ac:dyDescent="0.45">
@@ -87120,7 +87123,7 @@
         <v>0.4841333333333333</v>
       </c>
       <c r="S66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="8:19" x14ac:dyDescent="0.45">
@@ -87143,7 +87146,7 @@
         <v>0.58056666666666668</v>
       </c>
       <c r="S67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="8:19" x14ac:dyDescent="0.45">
@@ -87166,7 +87169,7 @@
         <v>0.53960000000000008</v>
       </c>
       <c r="S68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="8:19" x14ac:dyDescent="0.45">
@@ -87186,10 +87189,10 @@
         <v>44</v>
       </c>
       <c r="R69">
-        <v>0.40413333333333329</v>
+        <v>0.4041333333333334</v>
       </c>
       <c r="S69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="8:19" x14ac:dyDescent="0.45">
@@ -87212,7 +87215,7 @@
         <v>0.46510000000000001</v>
       </c>
       <c r="S70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="8:19" x14ac:dyDescent="0.45">
@@ -87235,7 +87238,7 @@
         <v>0.53883333333333328</v>
       </c>
       <c r="S71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="8:19" x14ac:dyDescent="0.45">
@@ -87258,7 +87261,7 @@
         <v>0.44576666666666664</v>
       </c>
       <c r="S72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="8:19" x14ac:dyDescent="0.45">
@@ -87281,7 +87284,7 @@
         <v>0.45049999999999996</v>
       </c>
       <c r="S73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="8:19" x14ac:dyDescent="0.45">
@@ -87301,10 +87304,10 @@
         <v>46</v>
       </c>
       <c r="R74">
-        <v>0.46470000000000006</v>
+        <v>0.46469999999999995</v>
       </c>
       <c r="S74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="8:19" x14ac:dyDescent="0.45">
@@ -87327,7 +87330,7 @@
         <v>0.56063333333333332</v>
       </c>
       <c r="S75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="8:19" x14ac:dyDescent="0.45">
@@ -87350,7 +87353,7 @@
         <v>0.49706666666666671</v>
       </c>
       <c r="S76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="8:19" x14ac:dyDescent="0.45">
@@ -87373,7 +87376,7 @@
         <v>0.39463333333333334</v>
       </c>
       <c r="S77" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="8:19" x14ac:dyDescent="0.45">
@@ -87396,7 +87399,7 @@
         <v>0.50383333333333336</v>
       </c>
       <c r="S78" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="8:19" x14ac:dyDescent="0.45">
@@ -87419,7 +87422,7 @@
         <v>0.60343333333333338</v>
       </c>
       <c r="S79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="8:19" x14ac:dyDescent="0.45">
@@ -87442,7 +87445,7 @@
         <v>0.45140000000000002</v>
       </c>
       <c r="S80" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="8:19" x14ac:dyDescent="0.45">
@@ -87465,7 +87468,7 @@
         <v>0.39076666666666665</v>
       </c>
       <c r="S81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="8:19" x14ac:dyDescent="0.45">
@@ -87485,10 +87488,10 @@
         <v>46</v>
       </c>
       <c r="R82">
-        <v>0.48076666666666662</v>
+        <v>0.48076666666666673</v>
       </c>
       <c r="S82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" spans="8:19" x14ac:dyDescent="0.45">
@@ -87511,7 +87514,7 @@
         <v>0.5806</v>
       </c>
       <c r="S83" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" spans="8:19" x14ac:dyDescent="0.45">
@@ -87531,10 +87534,10 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.4494333333333333</v>
+        <v>0.44943333333333335</v>
       </c>
       <c r="S84" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85" spans="8:19" x14ac:dyDescent="0.45">
@@ -87557,7 +87560,7 @@
         <v>0.38366666666666666</v>
       </c>
       <c r="S85" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="86" spans="8:19" x14ac:dyDescent="0.45">
@@ -87577,10 +87580,10 @@
         <v>46</v>
       </c>
       <c r="R86">
-        <v>0.48769999999999997</v>
+        <v>0.48770000000000002</v>
       </c>
       <c r="S86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="8:19" x14ac:dyDescent="0.45">
@@ -87603,7 +87606,7 @@
         <v>0.48920000000000002</v>
       </c>
       <c r="S87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="8:19" x14ac:dyDescent="0.45">
@@ -87626,7 +87629,7 @@
         <v>0.45343333333333335</v>
       </c>
       <c r="S88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="8:19" x14ac:dyDescent="0.45">
@@ -87649,7 +87652,7 @@
         <v>0.37609999999999993</v>
       </c>
       <c r="S89" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="8:19" x14ac:dyDescent="0.45">
@@ -87672,10 +87675,19 @@
         <v>0.46283333333333337</v>
       </c>
       <c r="S90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H91" t="s">
+        <v>267</v>
+      </c>
+      <c r="I91" t="s">
+        <v>38</v>
+      </c>
+      <c r="J91">
+        <v>0.406113</v>
+      </c>
       <c r="P91">
         <v>2042</v>
       </c>
@@ -87686,10 +87698,19 @@
         <v>0.46300000000000002</v>
       </c>
       <c r="S91" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H92" t="s">
+        <v>267</v>
+      </c>
+      <c r="I92" t="s">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>0.27523599999999998</v>
+      </c>
       <c r="P92">
         <v>2042</v>
       </c>
@@ -87700,10 +87721,19 @@
         <v>0.40473333333333333</v>
       </c>
       <c r="S92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H93" t="s">
+        <v>267</v>
+      </c>
+      <c r="I93" t="s">
+        <v>44</v>
+      </c>
+      <c r="J93">
+        <v>8.2413E-2</v>
+      </c>
       <c r="P93">
         <v>2042</v>
       </c>
@@ -87714,10 +87744,19 @@
         <v>0.37336666666666662</v>
       </c>
       <c r="S93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H94" t="s">
+        <v>267</v>
+      </c>
+      <c r="I94" t="s">
+        <v>46</v>
+      </c>
+      <c r="J94">
+        <v>0.236239</v>
+      </c>
       <c r="P94">
         <v>2042</v>
       </c>
@@ -87728,7 +87767,7 @@
         <v>0.40809999999999996</v>
       </c>
       <c r="S94" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="8:19" x14ac:dyDescent="0.45">
@@ -87742,7 +87781,7 @@
         <v>0.53733333333333333</v>
       </c>
       <c r="S95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="96" spans="8:19" x14ac:dyDescent="0.45">
@@ -87756,7 +87795,7 @@
         <v>0.43103333333333332</v>
       </c>
       <c r="S96" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -87770,7 +87809,7 @@
         <v>0.42219999999999996</v>
       </c>
       <c r="S97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -87784,7 +87823,7 @@
         <v>0.40806666666666663</v>
       </c>
       <c r="S98" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -87798,7 +87837,7 @@
         <v>0.5379666666666667</v>
       </c>
       <c r="S99" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -87809,10 +87848,10 @@
         <v>42</v>
       </c>
       <c r="R100">
-        <v>0.47149999999999997</v>
+        <v>0.47150000000000003</v>
       </c>
       <c r="S100" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -87826,7 +87865,7 @@
         <v>0.43759999999999999</v>
       </c>
       <c r="S101" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -87840,7 +87879,7 @@
         <v>0.44026666666666664</v>
       </c>
       <c r="S102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -87854,7 +87893,7 @@
         <v>0.4879</v>
       </c>
       <c r="S103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -87865,10 +87904,10 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.48726666666666668</v>
+        <v>0.48726666666666674</v>
       </c>
       <c r="S104" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -87882,7 +87921,7 @@
         <v>0.38966666666666666</v>
       </c>
       <c r="S105" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -87896,7 +87935,7 @@
         <v>0.45116666666666666</v>
       </c>
       <c r="S106" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -87910,7 +87949,7 @@
         <v>0.5623999999999999</v>
       </c>
       <c r="S107" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -87924,7 +87963,7 @@
         <v>0.45389999999999997</v>
       </c>
       <c r="S108" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -87938,7 +87977,7 @@
         <v>0.4237333333333333</v>
       </c>
       <c r="S109" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -87952,7 +87991,7 @@
         <v>0.43369999999999997</v>
       </c>
       <c r="S110" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -87966,7 +88005,7 @@
         <v>0.5672666666666667</v>
       </c>
       <c r="S111" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -87980,7 +88019,7 @@
         <v>0.54373333333333329</v>
       </c>
       <c r="S112" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -87994,7 +88033,7 @@
         <v>0.37453333333333338</v>
       </c>
       <c r="S113" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -88008,7 +88047,7 @@
         <v>0.51946666666666663</v>
       </c>
       <c r="S114" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -88022,7 +88061,7 @@
         <v>0.55986666666666662</v>
       </c>
       <c r="S115" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -88036,7 +88075,7 @@
         <v>0.48806666666666665</v>
       </c>
       <c r="S116" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -88050,7 +88089,7 @@
         <v>0.41326666666666667</v>
       </c>
       <c r="S117" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -88061,10 +88100,10 @@
         <v>46</v>
       </c>
       <c r="R118">
-        <v>0.49659999999999993</v>
+        <v>0.49659999999999999</v>
       </c>
       <c r="S118" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -88078,7 +88117,7 @@
         <v>0.58806666666666663</v>
       </c>
       <c r="S119" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -88092,7 +88131,7 @@
         <v>0.47560000000000002</v>
       </c>
       <c r="S120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -88106,7 +88145,7 @@
         <v>0.47403333333333331</v>
       </c>
       <c r="S121" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -88120,7 +88159,7 @@
         <v>0.48433333333333334</v>
       </c>
       <c r="S122" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -88134,7 +88173,7 @@
         <v>0.57599999999999996</v>
       </c>
       <c r="S123" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -88145,10 +88184,10 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.42926666666666663</v>
+        <v>0.42926666666666669</v>
       </c>
       <c r="S124" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -88159,10 +88198,10 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.42516666666666669</v>
+        <v>0.42516666666666664</v>
       </c>
       <c r="S125" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -88176,7 +88215,7 @@
         <v>0.48203333333333331</v>
       </c>
       <c r="S126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
